--- a/artfynd/A 66259-2021 artfynd.xlsx
+++ b/artfynd/A 66259-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128691745</v>
       </c>
       <c r="B2" t="n">
-        <v>56264</v>
+        <v>56291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 66259-2021 artfynd.xlsx
+++ b/artfynd/A 66259-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128691745</v>
       </c>
       <c r="B2" t="n">
-        <v>56291</v>
+        <v>56294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 66259-2021 artfynd.xlsx
+++ b/artfynd/A 66259-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128691745</v>
       </c>
       <c r="B2" t="n">
-        <v>56294</v>
+        <v>56297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 66259-2021 artfynd.xlsx
+++ b/artfynd/A 66259-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128691745</v>
       </c>
       <c r="B2" t="n">
-        <v>56297</v>
+        <v>56299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 66259-2021 artfynd.xlsx
+++ b/artfynd/A 66259-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128691745</v>
       </c>
       <c r="B2" t="n">
-        <v>56299</v>
+        <v>56522</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
